--- a/input_data/input_data_temps.xlsx
+++ b/input_data/input_data_temps.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsdennis\HOPE\Predicer\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9127071-4910-4078-B46C-52B268610842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95569EF8-2835-4F58-861B-7E3B4CA65F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="796" activeTab="2" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="796" firstSheet="5" activeTab="15" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
   </bookViews>
   <sheets>
     <sheet name="timeseries" sheetId="18" r:id="rId1"/>
@@ -28,20 +28,21 @@
     <sheet name="cf" sheetId="7" r:id="rId13"/>
     <sheet name="inflow" sheetId="3" r:id="rId14"/>
     <sheet name="inflow_blocks" sheetId="22" r:id="rId15"/>
-    <sheet name="price" sheetId="4" r:id="rId16"/>
-    <sheet name="markets" sheetId="5" r:id="rId17"/>
-    <sheet name="reserve_realisation" sheetId="23" r:id="rId18"/>
-    <sheet name="market_prices" sheetId="8" r:id="rId19"/>
-    <sheet name="balance_prices" sheetId="20" r:id="rId20"/>
-    <sheet name="reserve_activation_price" sheetId="28" r:id="rId21"/>
-    <sheet name="bid_slots" sheetId="29" r:id="rId22"/>
-    <sheet name="risk" sheetId="17" r:id="rId23"/>
-    <sheet name="scenarios" sheetId="9" r:id="rId24"/>
-    <sheet name="fixed_ts" sheetId="11" r:id="rId25"/>
-    <sheet name="eff_ts" sheetId="12" r:id="rId26"/>
-    <sheet name="constraints" sheetId="14" r:id="rId27"/>
-    <sheet name="gen_constraint" sheetId="15" r:id="rId28"/>
-    <sheet name="cap_ts" sheetId="16" r:id="rId29"/>
+    <sheet name="flex_inflow" sheetId="30" r:id="rId16"/>
+    <sheet name="price" sheetId="4" r:id="rId17"/>
+    <sheet name="markets" sheetId="5" r:id="rId18"/>
+    <sheet name="reserve_realisation" sheetId="23" r:id="rId19"/>
+    <sheet name="market_prices" sheetId="8" r:id="rId20"/>
+    <sheet name="balance_prices" sheetId="20" r:id="rId21"/>
+    <sheet name="reserve_activation_price" sheetId="28" r:id="rId22"/>
+    <sheet name="bid_slots" sheetId="29" r:id="rId23"/>
+    <sheet name="risk" sheetId="17" r:id="rId24"/>
+    <sheet name="scenarios" sheetId="9" r:id="rId25"/>
+    <sheet name="fixed_ts" sheetId="11" r:id="rId26"/>
+    <sheet name="eff_ts" sheetId="12" r:id="rId27"/>
+    <sheet name="constraints" sheetId="14" r:id="rId28"/>
+    <sheet name="gen_constraint" sheetId="15" r:id="rId29"/>
+    <sheet name="cap_ts" sheetId="16" r:id="rId30"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="136">
   <si>
     <t>node</t>
   </si>
@@ -454,6 +455,21 @@
   </si>
   <si>
     <t>common_end_timesteps</t>
+  </si>
+  <si>
+    <t>period_name</t>
+  </si>
+  <si>
+    <t>scenario</t>
+  </si>
+  <si>
+    <t>t_start</t>
+  </si>
+  <si>
+    <t>t_end</t>
+  </si>
+  <si>
+    <t>inflow</t>
   </si>
 </sst>
 </file>
@@ -506,12 +522,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -537,9 +550,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -577,7 +590,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -683,7 +696,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -825,7 +838,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -834,177 +847,177 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39053E69-3A75-490E-847C-66A9CF6C1FC5}">
   <dimension ref="A1:A49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <v>44624</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <v>44624.010416666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <v>44624.020833333336</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <v>44624.03125</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <v>44624.041666666664</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
         <v>44624.083333333336</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
         <v>44624.125</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
         <v>44624.291666666664</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
         <v>44624.458333333336</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="6"/>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="6"/>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="6"/>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="6"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="6"/>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="6"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="6"/>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="6"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="6"/>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="6"/>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="6"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="6"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="6"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="6"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="6"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="6"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="6"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="6"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="6"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="6"/>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="6"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="6"/>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="6"/>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="6"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="6"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="6"/>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="6"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="6"/>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3"/>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3"/>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3"/>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3"/>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3"/>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3"/>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3"/>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3"/>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1014,27 +1027,27 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7A97A19-79B8-46BB-9B8D-DDA080BD4E36}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>97</v>
       </c>
     </row>
@@ -1047,158 +1060,158 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA355BEF-1F4B-494A-B089-4FCDFFFA57F7}">
   <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44624</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44624.010416666664</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44624.020833333336</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44624.03125</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44624.041666666664</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44624.083333333336</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44624.125</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44624.291666666664</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44624.458333333336</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -1212,17 +1225,17 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0532F8A-0FB4-47AD-98A1-4065D3376432}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>48</v>
       </c>
@@ -1238,26 +1251,26 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77A4637A-7829-48D6-AE54-2E654AB1A427}">
   <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" customWidth="1"/>
-    <col min="9" max="9" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="23.109375" customWidth="1"/>
+    <col min="9" max="9" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44624</v>
       </c>
@@ -1267,10 +1280,10 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44624.010416666664</v>
       </c>
@@ -1281,8 +1294,8 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44624.020833333336</v>
       </c>
@@ -1293,8 +1306,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44624.03125</v>
       </c>
@@ -1305,8 +1318,8 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44624.041666666664</v>
       </c>
@@ -1317,8 +1330,8 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44624.083333333336</v>
       </c>
@@ -1329,8 +1342,8 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44624.125</v>
       </c>
@@ -1341,8 +1354,8 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44624.291666666664</v>
       </c>
@@ -1353,8 +1366,8 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44624.458333333336</v>
       </c>
@@ -1365,93 +1378,93 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
-      <c r="C11" s="6"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -1466,24 +1479,24 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F87DD44-A1AD-4241-AED7-C48CC9DEE2E2}">
   <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44624</v>
       </c>
@@ -1494,8 +1507,8 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44624.010416666664</v>
       </c>
@@ -1506,8 +1519,8 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44624.020833333336</v>
       </c>
@@ -1518,8 +1531,8 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44624.03125</v>
       </c>
@@ -1530,8 +1543,8 @@
         <v>-11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44624.041666666664</v>
       </c>
@@ -1542,8 +1555,8 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44624.083333333336</v>
       </c>
@@ -1554,8 +1567,8 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44624.125</v>
       </c>
@@ -1566,8 +1579,8 @@
         <v>-13</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44624.291666666664</v>
       </c>
@@ -1578,8 +1591,8 @@
         <v>-19</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44624.458333333336</v>
       </c>
@@ -1590,92 +1603,92 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -1690,86 +1703,86 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{098BD40C-3F1E-4DCA-B153-EDE213641CC0}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+    <col min="3" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="E2" s="6"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C2" s="3"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="E3" s="6"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C3" s="3"/>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="E4" s="6"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C4" s="3"/>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="E5" s="6"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C5" s="3"/>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-    </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1777,313 +1790,224 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02307C1F-427B-487D-B703-EBF512D7AC27}">
-  <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B91BAE62-FD1F-4244-B775-8F3666402775}">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
-        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
-        <v>44624</v>
-      </c>
-      <c r="B2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
-        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
-        <v>44624.010416666664</v>
-      </c>
-      <c r="B3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
-        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
-        <v>44624.020833333336</v>
-      </c>
-      <c r="B4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
-        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
-        <v>44624.03125</v>
-      </c>
-      <c r="B5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
-        <v>44624.041666666664</v>
-      </c>
-      <c r="B6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
-        <v>44624.083333333336</v>
-      </c>
-      <c r="B7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
-        <v>44624.125</v>
-      </c>
-      <c r="B8">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
-        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
-        <v>44624.291666666664</v>
-      </c>
-      <c r="B9">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
-        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
-        <v>44624.458333333336</v>
-      </c>
-      <c r="B10">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
-        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
-        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
-        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
-        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
-        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
-        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
-        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
-        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
-        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
-        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
-        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
-        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
-        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
-        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
-        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
-        <v/>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3788A93-7501-4F5D-9E8F-38D329CC85EC}">
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02307C1F-427B-487D-B703-EBF512D7AC27}">
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5">
-        <v>0</v>
-      </c>
-      <c r="J2" s="5">
-        <v>0</v>
-      </c>
-      <c r="K2" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E3" t="s">
-        <v>109</v>
-      </c>
-      <c r="F3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1000</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
+        <v>44624</v>
+      </c>
+      <c r="B2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
+        <v>44624.010416666664</v>
+      </c>
+      <c r="B3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
+        <v>44624.020833333336</v>
+      </c>
+      <c r="B4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
+        <v>44624.03125</v>
+      </c>
+      <c r="B5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
+        <v>44624.041666666664</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
+        <v>44624.083333333336</v>
+      </c>
+      <c r="B7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
+        <v>44624.125</v>
+      </c>
+      <c r="B8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
+        <v>44624.291666666664</v>
+      </c>
+      <c r="B9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
+        <v>44624.458333333336</v>
+      </c>
+      <c r="B10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
+        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
+        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
+        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
+        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
+        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
+        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
+        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
+        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
+        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
+        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
+        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
+        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
+        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
+        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
+        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2092,220 +2016,121 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E21372C5-DB60-4318-868D-D4FA20FECD5D}">
-  <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3788A93-7501-4F5D-9E8F-38D329CC85EC}">
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
-        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
-        <v>44624</v>
-      </c>
-      <c r="B2">
-        <v>0.2</v>
-      </c>
-      <c r="C2">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
-        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
-        <v>44624.010416666664</v>
-      </c>
-      <c r="B3">
-        <v>0.2</v>
-      </c>
-      <c r="C3">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
-        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
-        <v>44624.020833333336</v>
-      </c>
-      <c r="B4">
-        <v>0.2</v>
-      </c>
-      <c r="C4">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
-        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
-        <v>44624.03125</v>
-      </c>
-      <c r="B5">
-        <v>0.2</v>
-      </c>
-      <c r="C5">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
-        <v>44624.041666666664</v>
-      </c>
-      <c r="B6">
-        <v>0.2</v>
-      </c>
-      <c r="C6">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
-        <v>44624.083333333336</v>
-      </c>
-      <c r="B7">
-        <v>0.2</v>
-      </c>
-      <c r="C7">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
-        <v>44624.125</v>
-      </c>
-      <c r="B8">
-        <v>0.2</v>
-      </c>
-      <c r="C8">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
-        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
-        <v>44624.291666666664</v>
-      </c>
-      <c r="B9">
-        <v>0.2</v>
-      </c>
-      <c r="C9">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
-        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
-        <v>44624.458333333336</v>
-      </c>
-      <c r="B10">
-        <v>0.2</v>
-      </c>
-      <c r="C10">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
-        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
-        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
-        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
-        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
-        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
-        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
-        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
-        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
-        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
-        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
-        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
-        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
-        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
-        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
-        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
-        <v/>
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1000</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2314,285 +2139,223 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF6DDD9A-EF34-4108-8532-230729E9C708}">
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E21372C5-DB60-4318-868D-D4FA20FECD5D}">
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="B1" t="s">
         <v>110</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44624</v>
       </c>
       <c r="B2">
-        <v>70</v>
+        <v>0.2</v>
       </c>
       <c r="C2">
-        <v>57</v>
-      </c>
-      <c r="D2">
-        <v>30</v>
-      </c>
-      <c r="E2">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44624.010416666664</v>
       </c>
       <c r="B3">
-        <v>15</v>
+        <v>0.2</v>
       </c>
       <c r="C3">
-        <v>37</v>
-      </c>
-      <c r="D3">
-        <v>35</v>
-      </c>
-      <c r="E3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44624.020833333336</v>
       </c>
       <c r="B4">
-        <v>15</v>
+        <v>0.2</v>
       </c>
       <c r="C4">
-        <v>68</v>
-      </c>
-      <c r="D4">
-        <v>62</v>
-      </c>
-      <c r="E4">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44624.03125</v>
       </c>
       <c r="B5">
-        <v>18</v>
+        <v>0.2</v>
       </c>
       <c r="C5">
-        <v>51</v>
-      </c>
-      <c r="D5">
-        <v>24</v>
-      </c>
-      <c r="E5">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44624.041666666664</v>
       </c>
       <c r="B6">
-        <v>64</v>
+        <v>0.2</v>
       </c>
       <c r="C6">
-        <v>31</v>
-      </c>
-      <c r="D6">
-        <v>50</v>
-      </c>
-      <c r="E6">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44624.083333333336</v>
       </c>
       <c r="B7">
-        <v>42</v>
+        <v>0.2</v>
       </c>
       <c r="C7">
-        <v>66</v>
-      </c>
-      <c r="D7">
-        <v>67</v>
-      </c>
-      <c r="E7">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44624.125</v>
       </c>
       <c r="B8">
-        <v>56</v>
+        <v>0.2</v>
       </c>
       <c r="C8">
-        <v>19</v>
-      </c>
-      <c r="D8">
-        <v>19</v>
-      </c>
-      <c r="E8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44624.291666666664</v>
       </c>
       <c r="B9">
-        <v>37</v>
+        <v>0.2</v>
       </c>
       <c r="C9">
-        <v>60</v>
-      </c>
-      <c r="D9">
-        <v>54</v>
-      </c>
-      <c r="E9">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44624.458333333336</v>
       </c>
       <c r="B10">
-        <v>16</v>
+        <v>0.2</v>
       </c>
       <c r="C10">
-        <v>53</v>
-      </c>
-      <c r="D10">
-        <v>10</v>
-      </c>
-      <c r="E10">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2600,15 +2363,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C57021E-F1E6-4066-9417-B3D032BF6B3D}">
   <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.33203125" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>100</v>
       </c>
@@ -2620,7 +2383,7 @@
       </c>
       <c r="D1"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2631,7 +2394,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2642,7 +2405,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2653,23 +2416,23 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C6" s="9"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="8"/>
-      <c r="C7" s="9"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="8"/>
-      <c r="C8" s="9"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="8"/>
-      <c r="C9" s="9"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C10" s="9"/>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C6" s="6"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B7" s="5"/>
+      <c r="C7" s="6"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B8" s="5"/>
+      <c r="C8" s="6"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="5"/>
+      <c r="C9" s="6"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C10" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2678,316 +2441,279 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817FDE8F-BC70-48D0-8376-FB52E6946AF1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF6DDD9A-EF34-4108-8532-230729E9C708}">
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.28515625" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+      <c r="B1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44624</v>
       </c>
       <c r="B2">
-        <f>1.1*market_prices!B2</f>
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C2">
-        <f>1.1*market_prices!C2</f>
-        <v>62.7</v>
+        <v>57</v>
       </c>
       <c r="D2">
-        <f>0.9*market_prices!B2</f>
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <f>0.9*market_prices!C2</f>
-        <v>51.300000000000004</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44624.010416666664</v>
       </c>
       <c r="B3">
-        <f>1.1*market_prices!B3</f>
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="C3">
-        <f>1.1*market_prices!C3</f>
-        <v>40.700000000000003</v>
+        <v>37</v>
       </c>
       <c r="D3">
-        <f>0.9*market_prices!B3</f>
-        <v>13.5</v>
+        <v>35</v>
       </c>
       <c r="E3">
-        <f>0.9*market_prices!C3</f>
-        <v>33.300000000000004</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44624.020833333336</v>
       </c>
       <c r="B4">
-        <f>1.1*market_prices!B4</f>
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="C4">
-        <f>1.1*market_prices!C4</f>
-        <v>74.800000000000011</v>
+        <v>68</v>
       </c>
       <c r="D4">
-        <f>0.9*market_prices!B4</f>
-        <v>13.5</v>
+        <v>62</v>
       </c>
       <c r="E4">
-        <f>0.9*market_prices!C4</f>
-        <v>61.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44624.03125</v>
       </c>
       <c r="B5">
-        <f>1.1*market_prices!B5</f>
-        <v>19.8</v>
+        <v>18</v>
       </c>
       <c r="C5">
-        <f>1.1*market_prices!C5</f>
-        <v>56.1</v>
+        <v>51</v>
       </c>
       <c r="D5">
-        <f>0.9*market_prices!B5</f>
-        <v>16.2</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <f>0.9*market_prices!C5</f>
-        <v>45.9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44624.041666666664</v>
       </c>
       <c r="B6">
-        <f>1.1*market_prices!B6</f>
-        <v>70.400000000000006</v>
+        <v>64</v>
       </c>
       <c r="C6">
-        <f>1.1*market_prices!C6</f>
-        <v>34.1</v>
+        <v>31</v>
       </c>
       <c r="D6">
-        <f>0.9*market_prices!B6</f>
-        <v>57.6</v>
+        <v>50</v>
       </c>
       <c r="E6">
-        <f>0.9*market_prices!C6</f>
-        <v>27.900000000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44624.083333333336</v>
       </c>
       <c r="B7">
-        <f>1.1*market_prices!B7</f>
-        <v>46.2</v>
+        <v>42</v>
       </c>
       <c r="C7">
-        <f>1.1*market_prices!C7</f>
-        <v>72.600000000000009</v>
+        <v>66</v>
       </c>
       <c r="D7">
-        <f>0.9*market_prices!B7</f>
-        <v>37.800000000000004</v>
+        <v>67</v>
       </c>
       <c r="E7">
-        <f>0.9*market_prices!C7</f>
-        <v>59.4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44624.125</v>
       </c>
       <c r="B8">
-        <f>1.1*market_prices!B8</f>
-        <v>61.600000000000009</v>
+        <v>56</v>
       </c>
       <c r="C8">
-        <f>1.1*market_prices!C8</f>
-        <v>20.900000000000002</v>
+        <v>19</v>
       </c>
       <c r="D8">
-        <f>0.9*market_prices!B8</f>
-        <v>50.4</v>
+        <v>19</v>
       </c>
       <c r="E8">
-        <f>0.9*market_prices!C8</f>
-        <v>17.100000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44624.291666666664</v>
       </c>
       <c r="B9">
-        <f>1.1*market_prices!B9</f>
-        <v>40.700000000000003</v>
+        <v>37</v>
       </c>
       <c r="C9">
-        <f>1.1*market_prices!C9</f>
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D9">
-        <f>0.9*market_prices!B9</f>
-        <v>33.300000000000004</v>
+        <v>54</v>
       </c>
       <c r="E9">
-        <f>0.9*market_prices!C9</f>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44624.458333333336</v>
       </c>
       <c r="B10">
-        <f>1.1*market_prices!B10</f>
-        <v>17.600000000000001</v>
+        <v>16</v>
       </c>
       <c r="C10">
-        <f>1.1*market_prices!C10</f>
-        <v>58.300000000000004</v>
+        <v>53</v>
       </c>
       <c r="D10">
-        <f>0.9*market_prices!B10</f>
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E10">
-        <f>0.9*market_prices!C10</f>
-        <v>47.7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -2999,15 +2725,336 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817FDE8F-BC70-48D0-8376-FB52E6946AF1}">
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.33203125" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
+        <v>44624</v>
+      </c>
+      <c r="B2">
+        <f>1.1*market_prices!B2</f>
+        <v>77</v>
+      </c>
+      <c r="C2">
+        <f>1.1*market_prices!C2</f>
+        <v>62.7</v>
+      </c>
+      <c r="D2">
+        <f>0.9*market_prices!B2</f>
+        <v>63</v>
+      </c>
+      <c r="E2">
+        <f>0.9*market_prices!C2</f>
+        <v>51.300000000000004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
+        <v>44624.010416666664</v>
+      </c>
+      <c r="B3">
+        <f>1.1*market_prices!B3</f>
+        <v>16.5</v>
+      </c>
+      <c r="C3">
+        <f>1.1*market_prices!C3</f>
+        <v>40.700000000000003</v>
+      </c>
+      <c r="D3">
+        <f>0.9*market_prices!B3</f>
+        <v>13.5</v>
+      </c>
+      <c r="E3">
+        <f>0.9*market_prices!C3</f>
+        <v>33.300000000000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
+        <v>44624.020833333336</v>
+      </c>
+      <c r="B4">
+        <f>1.1*market_prices!B4</f>
+        <v>16.5</v>
+      </c>
+      <c r="C4">
+        <f>1.1*market_prices!C4</f>
+        <v>74.800000000000011</v>
+      </c>
+      <c r="D4">
+        <f>0.9*market_prices!B4</f>
+        <v>13.5</v>
+      </c>
+      <c r="E4">
+        <f>0.9*market_prices!C4</f>
+        <v>61.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
+        <v>44624.03125</v>
+      </c>
+      <c r="B5">
+        <f>1.1*market_prices!B5</f>
+        <v>19.8</v>
+      </c>
+      <c r="C5">
+        <f>1.1*market_prices!C5</f>
+        <v>56.1</v>
+      </c>
+      <c r="D5">
+        <f>0.9*market_prices!B5</f>
+        <v>16.2</v>
+      </c>
+      <c r="E5">
+        <f>0.9*market_prices!C5</f>
+        <v>45.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
+        <v>44624.041666666664</v>
+      </c>
+      <c r="B6">
+        <f>1.1*market_prices!B6</f>
+        <v>70.400000000000006</v>
+      </c>
+      <c r="C6">
+        <f>1.1*market_prices!C6</f>
+        <v>34.1</v>
+      </c>
+      <c r="D6">
+        <f>0.9*market_prices!B6</f>
+        <v>57.6</v>
+      </c>
+      <c r="E6">
+        <f>0.9*market_prices!C6</f>
+        <v>27.900000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
+        <v>44624.083333333336</v>
+      </c>
+      <c r="B7">
+        <f>1.1*market_prices!B7</f>
+        <v>46.2</v>
+      </c>
+      <c r="C7">
+        <f>1.1*market_prices!C7</f>
+        <v>72.600000000000009</v>
+      </c>
+      <c r="D7">
+        <f>0.9*market_prices!B7</f>
+        <v>37.800000000000004</v>
+      </c>
+      <c r="E7">
+        <f>0.9*market_prices!C7</f>
+        <v>59.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
+        <v>44624.125</v>
+      </c>
+      <c r="B8">
+        <f>1.1*market_prices!B8</f>
+        <v>61.600000000000009</v>
+      </c>
+      <c r="C8">
+        <f>1.1*market_prices!C8</f>
+        <v>20.900000000000002</v>
+      </c>
+      <c r="D8">
+        <f>0.9*market_prices!B8</f>
+        <v>50.4</v>
+      </c>
+      <c r="E8">
+        <f>0.9*market_prices!C8</f>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
+        <v>44624.291666666664</v>
+      </c>
+      <c r="B9">
+        <f>1.1*market_prices!B9</f>
+        <v>40.700000000000003</v>
+      </c>
+      <c r="C9">
+        <f>1.1*market_prices!C9</f>
+        <v>66</v>
+      </c>
+      <c r="D9">
+        <f>0.9*market_prices!B9</f>
+        <v>33.300000000000004</v>
+      </c>
+      <c r="E9">
+        <f>0.9*market_prices!C9</f>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
+        <v>44624.458333333336</v>
+      </c>
+      <c r="B10">
+        <f>1.1*market_prices!B10</f>
+        <v>17.600000000000001</v>
+      </c>
+      <c r="C10">
+        <f>1.1*market_prices!C10</f>
+        <v>58.300000000000004</v>
+      </c>
+      <c r="D10">
+        <f>0.9*market_prices!B10</f>
+        <v>14.4</v>
+      </c>
+      <c r="E10">
+        <f>0.9*market_prices!C10</f>
+        <v>47.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
+        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
+        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
+        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
+        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
+        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
+        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
+        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
+        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
+        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
+        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
+        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
+        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
+        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
+        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
+        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B32999EF-60F2-48CB-917A-DEA08B7B4CE6}">
   <dimension ref="A1:BA25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B1" t="s">
@@ -3067,8 +3114,8 @@
       <c r="AZ1"/>
       <c r="BA1"/>
     </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44624</v>
       </c>
@@ -3079,8 +3126,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44624.010416666664</v>
       </c>
@@ -3091,8 +3138,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44624.020833333336</v>
       </c>
@@ -3103,8 +3150,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+    <row r="5" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44624.03125</v>
       </c>
@@ -3115,8 +3162,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44624.041666666664</v>
       </c>
@@ -3127,8 +3174,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44624.083333333336</v>
       </c>
@@ -3139,8 +3186,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44624.125</v>
       </c>
@@ -3151,8 +3198,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44624.291666666664</v>
       </c>
@@ -3163,8 +3210,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44624.458333333336</v>
       </c>
@@ -3175,254 +3222,92 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
+    <row r="12" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
+    <row r="13" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
+    <row r="14" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
+    <row r="15" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
+    <row r="16" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
-        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5FC5C19-61CA-438C-ABFB-FA51A2F784B7}">
-  <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
-        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
-        <v>44624</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
-        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
-        <v>44624.010416666664</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
-        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
-        <v>44624.020833333336</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
-        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
-        <v>44624.03125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
-        <v>44624.041666666664</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
-        <v>44624.083333333336</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
-        <v>44624.125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
-        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
-        <v>44624.291666666664</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
-        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
-        <v>44624.458333333336</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
-        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
-        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
-        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
-        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
-        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
-        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
-        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
-        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
-        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
-        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
-        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
-        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
-        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
-        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -3433,35 +3318,160 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9314D326-256A-435C-AAE3-3517FA836EAE}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5FC5C19-61CA-438C-ABFB-FA51A2F784B7}">
+  <dimension ref="A1:A25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B3">
-        <v>0.2</v>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
+        <v>44624</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
+        <v>44624.010416666664</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
+        <v>44624.020833333336</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
+        <v>44624.03125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
+        <v>44624.041666666664</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
+        <v>44624.083333333336</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
+        <v>44624.125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
+        <v>44624.291666666664</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
+        <v>44624.458333333336</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
+        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
+        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
+        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
+        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
+        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
+        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
+        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
+        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
+        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
+        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
+        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
+        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
+        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
+        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
+        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3470,32 +3480,35 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87AD413-E614-48C1-80E1-F1E8236FCBC6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9314D326-256A-435C-AAE3-3517FA836EAE}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="B2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="B3">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -3504,167 +3517,32 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31679CA5-0AA2-4F6F-8223-14BF74917F04}">
-  <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87AD413-E614-48C1-80E1-F1E8236FCBC6}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
-        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
-        <v>44624</v>
-      </c>
-      <c r="B2" s="1"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
-        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
-        <v>44624.010416666664</v>
-      </c>
-      <c r="B3" s="1"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
-        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
-        <v>44624.020833333336</v>
-      </c>
-      <c r="B4" s="1"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
-        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
-        <v>44624.03125</v>
-      </c>
-      <c r="B5" s="1"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
-        <v>44624.041666666664</v>
-      </c>
-      <c r="B6" s="1"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
-        <v>44624.083333333336</v>
-      </c>
-      <c r="B7" s="1"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
-        <v>44624.125</v>
-      </c>
-      <c r="B8" s="1"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
-        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
-        <v>44624.291666666664</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
-        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
-        <v>44624.458333333336</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
-        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
-        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
-        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
-        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
-        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
-        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
-        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
-        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
-        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
-        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
-        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
-        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
-        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
-        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
-        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
-        <v/>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -3673,26 +3551,188 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31679CA5-0AA2-4F6F-8223-14BF74917F04}">
+  <dimension ref="A1:A25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
+        <v>44624</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
+        <v>44624.010416666664</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
+        <v>44624.020833333336</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
+        <v>44624.03125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
+        <v>44624.041666666664</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
+        <v>44624.083333333336</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
+        <v>44624.125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
+        <v>44624.291666666664</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
+        <v>44624.458333333336</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
+        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
+        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
+        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
+        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
+        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
+        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
+        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
+        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
+        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
+        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
+        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
+        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
+        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
+        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
+        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD670E02-665B-45B8-BC4E-9596D2C1BC55}">
   <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44624</v>
       </c>
@@ -3703,8 +3743,8 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44624.010416666664</v>
       </c>
@@ -3715,8 +3755,8 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44624.020833333336</v>
       </c>
@@ -3727,8 +3767,8 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44624.03125</v>
       </c>
@@ -3739,8 +3779,8 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44624.041666666664</v>
       </c>
@@ -3751,8 +3791,8 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44624.083333333336</v>
       </c>
@@ -3763,8 +3803,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44624.125</v>
       </c>
@@ -3775,8 +3815,8 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44624.291666666664</v>
       </c>
@@ -3787,8 +3827,8 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44624.458333333336</v>
       </c>
@@ -3799,92 +3839,92 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -3895,17 +3935,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5704FC51-737E-45F9-9A9E-85A96AFE5439}">
   <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>36</v>
       </c>
@@ -3919,7 +3959,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>53</v>
       </c>
@@ -3933,7 +3973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>104</v>
       </c>
@@ -3947,10 +3987,10 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3958,22 +3998,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE12AB76-2BDA-4ACA-A128-8CFB9FB6C8F8}">
   <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B1" t="s">
@@ -4001,8 +4041,8 @@
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44624</v>
       </c>
@@ -4034,8 +4074,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44624.010416666664</v>
       </c>
@@ -4067,8 +4107,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44624.020833333336</v>
       </c>
@@ -4100,8 +4140,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44624.03125</v>
       </c>
@@ -4133,8 +4173,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44624.041666666664</v>
       </c>
@@ -4166,8 +4206,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44624.083333333336</v>
       </c>
@@ -4199,8 +4239,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44624.125</v>
       </c>
@@ -4232,8 +4272,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44624.291666666664</v>
       </c>
@@ -4265,8 +4305,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44624.458333333336</v>
       </c>
@@ -4298,315 +4338,92 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
-        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7FEDBA5-B0F3-4E9D-9367-08D5F5FA8AEA}">
-  <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
-        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
-        <v>44624</v>
-      </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>5.9705000000000004</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
-        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
-        <v>44624.010416666664</v>
-      </c>
-      <c r="B3">
-        <v>4.2857142857142856</v>
-      </c>
-      <c r="C3">
-        <v>6.3089000000000004</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
-        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
-        <v>44624.020833333336</v>
-      </c>
-      <c r="B4">
-        <v>4.2857142857142856</v>
-      </c>
-      <c r="C4">
-        <v>6.0133000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
-        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
-        <v>44624.03125</v>
-      </c>
-      <c r="B5">
-        <v>4.4117647058823533</v>
-      </c>
-      <c r="C5">
-        <v>5.1531000000000002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
-        <v>44624.041666666664</v>
-      </c>
-      <c r="B6">
-        <v>4.5454545454545459</v>
-      </c>
-      <c r="C6">
-        <v>6.8680000000000003</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
-        <v>44624.083333333336</v>
-      </c>
-      <c r="B7">
-        <v>4.6875</v>
-      </c>
-      <c r="C7">
-        <v>6.1234000000000002</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
-        <v>44624.125</v>
-      </c>
-      <c r="B8">
-        <v>4.838709677419355</v>
-      </c>
-      <c r="C8">
-        <v>5.5724999999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
-        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
-        <v>44624.291666666664</v>
-      </c>
-      <c r="B9">
-        <v>5</v>
-      </c>
-      <c r="C9">
-        <v>4.9116999999999997</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
-        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
-        <v>44624.458333333336</v>
-      </c>
-      <c r="B10">
-        <v>6</v>
-      </c>
-      <c r="C10">
-        <v>5.7545000000000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
-        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
-        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
-        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
-        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
-        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
-        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
-        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
-        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
-        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
-        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
-        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
-        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
-        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
-        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -4620,21 +4437,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A8722DB-EA8F-4752-8AE5-4F3986218151}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>115</v>
       </c>
@@ -4642,7 +4459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>116</v>
       </c>
@@ -4650,7 +4467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>117</v>
       </c>
@@ -4658,7 +4475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>118</v>
       </c>
@@ -4666,7 +4483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>119</v>
       </c>
@@ -4674,7 +4491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>123</v>
       </c>
@@ -4682,7 +4499,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>124</v>
       </c>
@@ -4690,7 +4507,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>129</v>
       </c>
@@ -4698,7 +4515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>130</v>
       </c>
@@ -4706,7 +4523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>120</v>
       </c>
@@ -4717,269 +4534,492 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7FEDBA5-B0F3-4E9D-9367-08D5F5FA8AEA}">
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
+        <v>44624</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>5.9705000000000004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
+        <v>44624.010416666664</v>
+      </c>
+      <c r="B3">
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="C3">
+        <v>6.3089000000000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
+        <v>44624.020833333336</v>
+      </c>
+      <c r="B4">
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="C4">
+        <v>6.0133000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
+        <v>44624.03125</v>
+      </c>
+      <c r="B5">
+        <v>4.4117647058823533</v>
+      </c>
+      <c r="C5">
+        <v>5.1531000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
+        <v>44624.041666666664</v>
+      </c>
+      <c r="B6">
+        <v>4.5454545454545459</v>
+      </c>
+      <c r="C6">
+        <v>6.8680000000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
+        <v>44624.083333333336</v>
+      </c>
+      <c r="B7">
+        <v>4.6875</v>
+      </c>
+      <c r="C7">
+        <v>6.1234000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
+        <v>44624.125</v>
+      </c>
+      <c r="B8">
+        <v>4.838709677419355</v>
+      </c>
+      <c r="C8">
+        <v>5.5724999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
+        <v>44624.291666666664</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>4.9116999999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
+        <v>44624.458333333336</v>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10">
+        <v>5.7545000000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
+        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
+        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
+        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
+        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
+        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
+        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
+        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
+        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
+        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
+        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
+        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
+        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
+        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
+        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
+        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04A1B16B-CDA9-46BD-BA51-731AA9327652}">
   <dimension ref="A1:P7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5">
-        <v>1</v>
-      </c>
-      <c r="C2" s="5">
-        <v>0</v>
-      </c>
-      <c r="D2" s="5">
-        <v>0</v>
-      </c>
-      <c r="E2" s="5">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5">
-        <v>0</v>
-      </c>
-      <c r="H2" s="5">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5">
-        <v>0</v>
-      </c>
-      <c r="J2" s="5">
-        <v>0</v>
-      </c>
-      <c r="K2" s="5">
-        <v>0</v>
-      </c>
-      <c r="L2" s="5">
-        <v>0</v>
-      </c>
-      <c r="M2" s="5">
-        <v>0</v>
-      </c>
-      <c r="N2" s="5">
-        <v>0</v>
-      </c>
-      <c r="O2" s="5">
-        <v>1</v>
-      </c>
-      <c r="P2" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2">
+        <v>0</v>
+      </c>
+      <c r="O2" s="2">
+        <v>1</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="5">
-        <v>0</v>
-      </c>
-      <c r="C3" s="5">
-        <v>0</v>
-      </c>
-      <c r="D3" s="5">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5">
-        <v>0</v>
-      </c>
-      <c r="G3" s="5">
-        <v>0</v>
-      </c>
-      <c r="H3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-      <c r="N3" s="5">
-        <v>0</v>
-      </c>
-      <c r="O3" s="5">
-        <v>1</v>
-      </c>
-      <c r="P3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2">
+        <v>1</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="5">
-        <v>0</v>
-      </c>
-      <c r="C4" s="5">
-        <v>1</v>
-      </c>
-      <c r="D4" s="5">
-        <v>0</v>
-      </c>
-      <c r="E4" s="5">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5">
-        <v>1</v>
-      </c>
-      <c r="G4" s="5">
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2">
         <v>10</v>
       </c>
-      <c r="H4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5">
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
         <v>3</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="2">
         <v>3</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="2">
         <v>10</v>
       </c>
       <c r="L4">
         <v>1E-3</v>
       </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-      <c r="N4" s="5">
-        <v>0</v>
-      </c>
-      <c r="O4" s="5">
-        <v>1</v>
-      </c>
-      <c r="P4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
+      <c r="M4" s="2">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2">
+        <v>1</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4989,250 +5029,250 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB20090B-02A9-43B7-8D03-9C18D42920EB}">
   <dimension ref="A1:Q5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
     <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="11.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="5">
-        <v>0</v>
-      </c>
-      <c r="C2" s="5">
-        <v>0</v>
-      </c>
-      <c r="D2" s="5">
-        <v>0</v>
-      </c>
-      <c r="E2" s="5">
-        <v>1</v>
-      </c>
-      <c r="F2" s="5">
-        <v>1</v>
-      </c>
-      <c r="G2" s="5">
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2">
         <v>0.9</v>
       </c>
-      <c r="H2" s="5">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5">
-        <v>1</v>
-      </c>
-      <c r="J2" s="5">
-        <v>0</v>
-      </c>
-      <c r="K2" s="5">
-        <v>0</v>
-      </c>
-      <c r="L2" s="5">
-        <v>0</v>
-      </c>
-      <c r="M2" s="5">
-        <v>0</v>
-      </c>
-      <c r="N2" s="5">
-        <v>0</v>
-      </c>
-      <c r="O2" s="5">
-        <v>0</v>
-      </c>
-      <c r="P2" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H2" s="2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2">
+        <v>0</v>
+      </c>
+      <c r="O2" s="2">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="5">
-        <v>0</v>
-      </c>
-      <c r="C3" s="5">
-        <v>0</v>
-      </c>
-      <c r="D3" s="5">
-        <v>0</v>
-      </c>
-      <c r="E3" s="5">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5">
-        <v>1</v>
-      </c>
-      <c r="G3" s="5">
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2">
         <v>3</v>
       </c>
-      <c r="H3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-      <c r="N3" s="5">
-        <v>0</v>
-      </c>
-      <c r="O3" s="5">
-        <v>0</v>
-      </c>
-      <c r="P3" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="5">
-        <v>1</v>
-      </c>
-      <c r="C4" s="5">
-        <v>1</v>
-      </c>
-      <c r="D4" s="5">
-        <v>0</v>
-      </c>
-      <c r="E4" s="5">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5">
-        <v>1</v>
-      </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5">
-        <v>1</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-      <c r="N4" s="5">
-        <v>0</v>
-      </c>
-      <c r="O4" s="5">
-        <v>0</v>
-      </c>
-      <c r="P4" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5242,20 +5282,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6007B83A-95ED-43FB-AC05-C8A15D3323E5}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -5266,7 +5306,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -5277,7 +5317,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -5296,48 +5336,48 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAB1106B-D567-41FC-8E91-2B4CC5EC9B59}">
   <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="2">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2">
+      <c r="B1" s="1">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1">
         <f>B1+1</f>
         <v>2</v>
       </c>
-      <c r="D1" s="2">
+      <c r="D1" s="1">
         <f t="shared" ref="D1:K1" si="0">C1+1</f>
         <v>3</v>
       </c>
-      <c r="E1" s="2">
+      <c r="E1" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F1" s="2">
+      <c r="F1" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G1" s="2">
+      <c r="G1" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H1" s="2">
+      <c r="H1" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="I1" s="2">
+      <c r="I1" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="J1" s="2">
+      <c r="J1" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K1" s="2">
+      <c r="K1" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -5350,273 +5390,272 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A86A8A7-FD76-4891-A53C-CBB095359118}">
   <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L1" s="4"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="L1"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4">
-        <v>1</v>
-      </c>
-      <c r="E2" s="4">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
         <v>20</v>
       </c>
-      <c r="F2" s="4">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4">
-        <v>1</v>
-      </c>
-      <c r="H2" s="4">
-        <v>1</v>
-      </c>
-      <c r="I2" s="4">
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
         <v>0.7</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2">
         <v>0.7</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="4">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4">
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>10</v>
       </c>
-      <c r="F3" s="4">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4">
-        <v>1</v>
-      </c>
-      <c r="H3" s="4">
-        <v>1</v>
-      </c>
-      <c r="I3" s="4">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
         <v>0.7</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3">
         <v>0.7</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
         <v>8</v>
       </c>
-      <c r="F4" s="4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4">
-        <v>1</v>
-      </c>
-      <c r="H4" s="4">
-        <v>1</v>
-      </c>
-      <c r="I4" s="4">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
         <v>0.7</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4">
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="4">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4">
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
         <v>5</v>
       </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4">
-        <v>1</v>
-      </c>
-      <c r="H5" s="4">
-        <v>1</v>
-      </c>
-      <c r="I5" s="4">
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
         <v>0.7</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5">
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
         <v>15</v>
       </c>
-      <c r="F6" s="4">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4">
-        <v>1</v>
-      </c>
-      <c r="H6" s="4">
-        <v>1</v>
-      </c>
-      <c r="I6" s="4">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
         <v>0.7</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6">
         <v>0.7</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="4">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4">
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
         <v>5</v>
       </c>
-      <c r="F7" s="4">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4">
-        <v>1</v>
-      </c>
-      <c r="I7" s="4">
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
         <v>0.7</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7">
         <v>0.7</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="4">
-        <v>1</v>
-      </c>
-      <c r="E8" s="4">
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
         <v>5</v>
       </c>
-      <c r="F8" s="4">
-        <v>0</v>
-      </c>
-      <c r="G8" s="4">
-        <v>1</v>
-      </c>
-      <c r="H8" s="4">
-        <v>1</v>
-      </c>
-      <c r="I8" s="4">
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
         <v>0.7</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8">
         <v>0.7</v>
       </c>
     </row>
@@ -5629,156 +5668,156 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7AEF404-3743-47D7-AC45-7AE3A9FB796E}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44624</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44624.010416666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44624.020833333336</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44624.03125</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44624.041666666664</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44624.083333333336</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44624.125</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44624.291666666664</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44624.458333333336</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="str">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="str">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="str">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="str">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="str">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="str">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="str">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>

--- a/input_data/input_data_temps.xlsx
+++ b/input_data/input_data_temps.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsdennis\HOPE\Predicer\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95569EF8-2835-4F58-861B-7E3B4CA65F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A462AE49-F903-48AC-9AC3-D7C72F6796F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="796" firstSheet="5" activeTab="15" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="137">
   <si>
     <t>node</t>
   </si>
@@ -470,6 +470,9 @@
   </si>
   <si>
     <t>inflow</t>
+  </si>
+  <si>
+    <t>deviation_penalty</t>
   </si>
 </sst>
 </file>
@@ -1791,13 +1794,13 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B91BAE62-FD1F-4244-B775-8F3666402775}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>131</v>
       </c>
@@ -1815,6 +1818,9 @@
       </c>
       <c r="F1" t="s">
         <v>135</v>
+      </c>
+      <c r="G1" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
